--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/close/close_annual_metrics.xlsx
@@ -466,18 +466,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -560,43 +560,43 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-0.03599785872987094</v>
+        <v>0.05609583892475856</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>-0.02176047699359285</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>-0.0145540855807208</v>
+        <v>0.07958819296022068</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.3070625359146133</v>
+        <v>0.240729633413871</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2786573063505097</v>
+        <v>0.2136148574836628</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.03041445765961466</v>
+        <v>0.3142603726934849</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.04310923963405018</v>
+        <v>0.4505042551518341</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.05122015530352562</v>
+        <v>0.4646858204971295</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.2025006465945796</v>
+        <v>0.1880124217731213</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.1506490308477421</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.2026577108627408</v>
+        <v>0.1329739179608295</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>-0.200409074162253</v>
+        <v>0.3383732013512707</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>25.04332584195137</v>
+        <v>18.71363541901007</v>
       </c>
     </row>
     <row r="3">
@@ -606,43 +606,43 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.2452137539097202</v>
+        <v>-0.1274051094365372</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-0.2255774308756096</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-0.02535608312179383</v>
+        <v>0.1267684147558776</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.2387495327535568</v>
+        <v>0.164531409270536</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.2160191954884186</v>
+        <v>0.1680236893515153</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-1.169796981045222</v>
+        <v>-0.8708895599511965</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-1.586685060312226</v>
+        <v>-1.201547121223481</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>-0.09265260989947702</v>
+        <v>0.6902898884113061</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.2796914185356542</v>
+        <v>0.1587925230256801</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.2845881262232945</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1815738597145996</v>
+        <v>0.1000647302509236</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-0.9079191929310466</v>
+        <v>-0.8331964928737362</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>21.55776910988066</v>
+        <v>16.06058234832611</v>
       </c>
     </row>
     <row r="4">
@@ -652,43 +652,43 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.1363714032782523</v>
+        <v>-0.1086314250867472</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.1141699148043651</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.02506291990408538</v>
+        <v>0.006252316115901602</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.2599017290914829</v>
+        <v>0.1677331710886439</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.232677061324856</v>
+        <v>0.1454496864905748</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.5154751776625178</v>
+        <v>-0.7188439623651282</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.7494205764679632</v>
+        <v>-0.9887384432285439</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.00857187488899434</v>
+        <v>0.07840810295814894</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.2546559262343742</v>
+        <v>0.1996045349055364</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.2177913835362562</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.1385429282671164</v>
+        <v>0.07536372651940437</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-0.5559963461196642</v>
+        <v>-0.5654035815608298</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>24.33972308421173</v>
+        <v>17.42064379051267</v>
       </c>
     </row>
     <row r="5">
@@ -698,43 +698,43 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.2229918765730675</v>
+        <v>0.01936756105648296</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0.1298071537204202</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.3122648224803084</v>
+        <v>-0.09775083499893222</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.2623711947970778</v>
+        <v>0.2203086095469252</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1898931220878438</v>
+        <v>0.1329720030415862</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.927012599705204</v>
+        <v>0.130462106751315</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-1.300984764734328</v>
+        <v>0.2303399725664384</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-2.006793580856892</v>
+        <v>-0.8205710017550856</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.3100415625593977</v>
+        <v>0.1857786397669768</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.1515696200238076</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.3946489551753199</v>
+        <v>0.1755194333255026</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-0.7452250163073882</v>
+        <v>0.1086017980470809</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>24.17271383316537</v>
+        <v>16.86462393499667</v>
       </c>
     </row>
     <row r="6">
@@ -744,43 +744,43 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.3458765186748491</v>
+        <v>0.2005617469130951</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.2243203183030871</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.09928463863136416</v>
+        <v>-0.01940551915606881</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.3361987503880586</v>
+        <v>0.2248340208166821</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.259250958987474</v>
+        <v>0.1448800769755679</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.040030815519885</v>
+        <v>0.8894867347769365</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.55089089950179</v>
+        <v>1.282835802223756</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.5420876453003598</v>
+        <v>-0.06304137733181059</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.2407896440629005</v>
+        <v>0.153553250270975</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.1188658802983931</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2097905499764001</v>
+        <v>0.1627179817370054</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.498258694673025</v>
+        <v>1.359249023466864</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>24.35767419241175</v>
+        <v>19.36109774538191</v>
       </c>
     </row>
     <row r="7">
@@ -790,43 +790,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.232629276512845</v>
+        <v>0.1322714488086705</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-0.01504143451691176</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.2514529237159178</v>
+        <v>0.1495625181484972</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.4831133074212285</v>
+        <v>0.273849109937107</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.4176928167650691</v>
+        <v>0.2102292092856859</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.002309092330719</v>
+        <v>0.9110762699902171</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.425630518291349</v>
+        <v>1.273094991894434</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.198374995262452</v>
+        <v>1.264435104820026</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.2796809875763159</v>
+        <v>0.1182545718746322</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.127969093077366</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.2452456613660888</v>
+        <v>0.09307390677556848</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.662974973288945</v>
+        <v>2.15330290886868</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>24.27030921044835</v>
+        <v>18.91372439353854</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/close/close_annual_metrics.xlsx
@@ -466,18 +466,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -560,43 +560,43 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.05609583892475856</v>
+        <v>-0.004198631604396375</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>-0.02176047699359285</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.07958819296022068</v>
+        <v>0.01795250036026541</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.240729633413871</v>
+        <v>0.2653392417240657</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2136148574836628</v>
+        <v>0.2581971227994144</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.3142603726934849</v>
+        <v>0.05804317653622791</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.4505042551518341</v>
+        <v>0.08347202383600022</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.4646858204971295</v>
+        <v>0.1510982889025106</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1880124217731213</v>
+        <v>0.1739826211445832</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.1506490308477421</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1329739179608295</v>
+        <v>0.1886245409480094</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.3383732013512707</v>
+        <v>-0.02726332704440066</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>18.71363541901007</v>
+        <v>19.96616888909875</v>
       </c>
     </row>
     <row r="3">
@@ -606,43 +606,43 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.1274051094365372</v>
+        <v>-0.1861960348175978</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-0.2255774308756096</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.1267684147558776</v>
+        <v>0.05085259343944415</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.164531409270536</v>
+        <v>0.2102376467431641</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.1680236893515153</v>
+        <v>0.1966040531874684</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.8708895599511965</v>
+        <v>-0.9860284414528002</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-1.201547121223481</v>
+        <v>-1.325980383503691</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.6902898884113061</v>
+        <v>0.2643558990528846</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.1587925230256801</v>
+        <v>0.2467390836645724</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.2845881262232945</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1000647302509236</v>
+        <v>0.1410415404034365</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-0.8331964928737362</v>
+        <v>-0.7825888215710416</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>16.06058234832611</v>
+        <v>17.07620088268751</v>
       </c>
     </row>
     <row r="4">
@@ -652,43 +652,43 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.1086314250867472</v>
+        <v>-0.09482547969825561</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.1141699148043651</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.006252316115901602</v>
+        <v>0.02183763616680423</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.1677331710886439</v>
+        <v>0.1709994785953133</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1454496864905748</v>
+        <v>0.1464599271962971</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.7188439623651282</v>
+        <v>-0.6084514976446124</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.9887384432285439</v>
+        <v>-0.8590021449758142</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.07840810295814894</v>
+        <v>0.1907246781149038</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.1996045349055364</v>
+        <v>0.183078281284742</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.2177913835362562</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.07536372651940437</v>
+        <v>0.07067868714344672</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-0.5654035815608298</v>
+        <v>-0.5382630700202715</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>17.42064379051267</v>
+        <v>16.12581805139804</v>
       </c>
     </row>
     <row r="5">
@@ -698,43 +698,43 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.01936756105648296</v>
+        <v>-0.04877185875361467</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0.1298071537204202</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.09775083499893222</v>
+        <v>-0.158061499155837</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.2203086095469252</v>
+        <v>0.2250959707548032</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1329720030415862</v>
+        <v>0.1679305428693688</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.130462106751315</v>
+        <v>-0.1871765283830718</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.2303399725664384</v>
+        <v>-0.300233772579153</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.8205710017550856</v>
+        <v>-1.071797746625944</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.1857786397669768</v>
+        <v>0.2244944302510938</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.1515696200238076</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1755194333255026</v>
+        <v>0.2557223110826015</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.1086017980470809</v>
+        <v>-0.2259977233898361</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>16.86462393499667</v>
+        <v>18.48484853364112</v>
       </c>
     </row>
     <row r="6">
@@ -744,43 +744,43 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.2005617469130951</v>
+        <v>0.02946068166100857</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.2243203183030871</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.01940551915606881</v>
+        <v>-0.1591573983777012</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.2248340208166821</v>
+        <v>0.1812599374470209</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1448800769755679</v>
+        <v>0.1325962795883737</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.8894867347769365</v>
+        <v>0.1747734545593596</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.282835802223756</v>
+        <v>0.2318672753682317</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.06304137733181059</v>
+        <v>-1.338204161937948</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.153553250270975</v>
+        <v>0.1250378887661396</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.1188658802983931</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1627179817370054</v>
+        <v>0.247127769540009</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.359249023466864</v>
+        <v>0.2444725437853757</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>19.36109774538191</v>
+        <v>18.63427185440939</v>
       </c>
     </row>
     <row r="7">
@@ -790,43 +790,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.1322714488086705</v>
+        <v>0.08648394511729718</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-0.01504143451691176</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.1495625181484972</v>
+        <v>0.1030757873397601</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.273849109937107</v>
+        <v>0.2950668287479916</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2102292092856859</v>
+        <v>0.2711808501437302</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.9110762699902171</v>
+        <v>0.6105227593998787</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.273094991894434</v>
+        <v>0.8430069931976338</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.264435104820026</v>
+        <v>0.7244935660029116</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1182545718746322</v>
+        <v>0.1486070005630952</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.127969093077366</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.09307390677556848</v>
+        <v>0.1351974573920616</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.15330290886868</v>
+        <v>1.10049344270104</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>18.91372439353854</v>
+        <v>20.81412922412416</v>
       </c>
     </row>
   </sheetData>
